--- a/data/initial/paleamia 2026.xlsx
+++ b/data/initial/paleamia 2026.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://natuaromatic-my.sharepoint.com/personal/digitalmanager_natuaromatic_com/Documents/TRANSPORTE/tarifas/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="108" documentId="8_{402BB4B8-1360-435E-B291-2B3970E20386}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{6E6A8843-CE05-4430-87FC-BE0E2C1DEB51}"/>
+  <xr:revisionPtr revIDLastSave="110" documentId="8_{402BB4B8-1360-435E-B291-2B3970E20386}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{4E3DD716-FFAB-4E73-BC57-364E479BDC7F}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView minimized="1" xWindow="-22605" yWindow="1215" windowWidth="21600" windowHeight="13410" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Tarifas 2026" sheetId="1" r:id="rId1"/>
@@ -375,6 +375,72 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="5" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="6" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="5" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="6" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="8" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="9" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="2" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="3" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="10" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="11" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="7" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="2" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="3" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="8" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="10" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="11" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" shrinkToFit="1"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="4" borderId="7" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -396,30 +462,6 @@
     <xf numFmtId="0" fontId="4" fillId="4" borderId="11" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" shrinkToFit="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="9" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="2" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="3" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="10" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="11" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="5" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="6" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" shrinkToFit="1"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="3" borderId="10" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" shrinkToFit="1"/>
     </xf>
@@ -434,48 +476,6 @@
     </xf>
     <xf numFmtId="0" fontId="4" fillId="4" borderId="3" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="7" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="2" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="3" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="8" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="10" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="11" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="5" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="6" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
-      <alignment vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="8" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" shrinkToFit="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -855,7 +855,7 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>5</xdr:col>
-      <xdr:colOff>710102</xdr:colOff>
+      <xdr:colOff>329102</xdr:colOff>
       <xdr:row>36</xdr:row>
       <xdr:rowOff>104775</xdr:rowOff>
     </xdr:to>
@@ -1331,11 +1331,11 @@
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="15.5703125" customWidth="1"/>
-    <col min="2" max="2" width="12.42578125" style="11" customWidth="1"/>
+    <col min="2" max="2" width="18.140625" style="11" customWidth="1"/>
     <col min="3" max="3" width="16.140625" style="11" customWidth="1"/>
     <col min="4" max="4" width="23.5703125" customWidth="1"/>
     <col min="5" max="6" width="24.5703125" customWidth="1"/>
-    <col min="7" max="7" width="12.85546875" customWidth="1"/>
+    <col min="7" max="7" width="20" customWidth="1"/>
     <col min="8" max="8" width="18.42578125" customWidth="1"/>
     <col min="9" max="10" width="19.42578125" customWidth="1"/>
     <col min="11" max="11" width="13.28515625" customWidth="1"/>
@@ -2341,326 +2341,316 @@
       <c r="G19" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="H19" s="39" t="s">
+      <c r="H19" s="14" t="s">
         <v>20</v>
       </c>
-      <c r="I19" s="39"/>
-      <c r="J19" s="39"/>
-      <c r="K19" s="39"/>
-      <c r="L19" s="39"/>
-      <c r="M19" s="39"/>
-      <c r="N19" s="39"/>
-      <c r="O19" s="39"/>
-      <c r="P19" s="39"/>
+      <c r="I19" s="14"/>
+      <c r="J19" s="14"/>
+      <c r="K19" s="14"/>
+      <c r="L19" s="14"/>
+      <c r="M19" s="14"/>
+      <c r="N19" s="14"/>
+      <c r="O19" s="14"/>
+      <c r="P19" s="14"/>
     </row>
     <row r="20" spans="7:16" ht="20.25" thickBot="1">
       <c r="G20" s="2">
         <v>0</v>
       </c>
-      <c r="H20" s="40" t="s">
+      <c r="H20" s="15" t="s">
         <v>21</v>
       </c>
-      <c r="I20" s="40"/>
-      <c r="J20" s="40"/>
-      <c r="K20" s="40"/>
-      <c r="L20" s="40"/>
-      <c r="M20" s="40"/>
-      <c r="N20" s="40"/>
-      <c r="O20" s="40"/>
-      <c r="P20" s="41"/>
+      <c r="I20" s="15"/>
+      <c r="J20" s="15"/>
+      <c r="K20" s="15"/>
+      <c r="L20" s="15"/>
+      <c r="M20" s="15"/>
+      <c r="N20" s="15"/>
+      <c r="O20" s="15"/>
+      <c r="P20" s="16"/>
     </row>
     <row r="21" spans="7:16" ht="20.25" thickBot="1">
       <c r="G21" s="3">
         <v>1</v>
       </c>
-      <c r="H21" s="42" t="s">
+      <c r="H21" s="17" t="s">
         <v>22</v>
       </c>
-      <c r="I21" s="42"/>
-      <c r="J21" s="42"/>
-      <c r="K21" s="42"/>
-      <c r="L21" s="42"/>
-      <c r="M21" s="42"/>
-      <c r="N21" s="42"/>
-      <c r="O21" s="42"/>
-      <c r="P21" s="43"/>
+      <c r="I21" s="17"/>
+      <c r="J21" s="17"/>
+      <c r="K21" s="17"/>
+      <c r="L21" s="17"/>
+      <c r="M21" s="17"/>
+      <c r="N21" s="17"/>
+      <c r="O21" s="17"/>
+      <c r="P21" s="18"/>
     </row>
     <row r="22" spans="7:16" ht="20.25" thickBot="1">
       <c r="G22" s="4">
         <v>2</v>
       </c>
-      <c r="H22" s="44" t="s">
+      <c r="H22" s="19" t="s">
         <v>23</v>
       </c>
-      <c r="I22" s="44"/>
-      <c r="J22" s="44"/>
-      <c r="K22" s="44"/>
-      <c r="L22" s="44"/>
-      <c r="M22" s="44"/>
-      <c r="N22" s="44"/>
-      <c r="O22" s="44"/>
-      <c r="P22" s="45"/>
+      <c r="I22" s="19"/>
+      <c r="J22" s="19"/>
+      <c r="K22" s="19"/>
+      <c r="L22" s="19"/>
+      <c r="M22" s="19"/>
+      <c r="N22" s="19"/>
+      <c r="O22" s="19"/>
+      <c r="P22" s="20"/>
     </row>
     <row r="23" spans="7:16">
-      <c r="G23" s="19">
+      <c r="G23" s="21">
         <v>3</v>
       </c>
-      <c r="H23" s="21" t="s">
+      <c r="H23" s="23" t="s">
         <v>24</v>
       </c>
-      <c r="I23" s="21"/>
-      <c r="J23" s="21"/>
-      <c r="K23" s="21"/>
-      <c r="L23" s="21"/>
-      <c r="M23" s="21"/>
-      <c r="N23" s="21"/>
-      <c r="O23" s="21"/>
-      <c r="P23" s="22"/>
+      <c r="I23" s="23"/>
+      <c r="J23" s="23"/>
+      <c r="K23" s="23"/>
+      <c r="L23" s="23"/>
+      <c r="M23" s="23"/>
+      <c r="N23" s="23"/>
+      <c r="O23" s="23"/>
+      <c r="P23" s="24"/>
     </row>
     <row r="24" spans="7:16" ht="15.75" thickBot="1">
-      <c r="G24" s="20"/>
-      <c r="H24" s="23"/>
-      <c r="I24" s="23"/>
-      <c r="J24" s="23"/>
-      <c r="K24" s="23"/>
-      <c r="L24" s="23"/>
-      <c r="M24" s="23"/>
-      <c r="N24" s="23"/>
-      <c r="O24" s="23"/>
-      <c r="P24" s="24"/>
+      <c r="G24" s="22"/>
+      <c r="H24" s="25"/>
+      <c r="I24" s="25"/>
+      <c r="J24" s="25"/>
+      <c r="K24" s="25"/>
+      <c r="L24" s="25"/>
+      <c r="M24" s="25"/>
+      <c r="N24" s="25"/>
+      <c r="O24" s="25"/>
+      <c r="P24" s="26"/>
     </row>
     <row r="25" spans="7:16" ht="20.25" thickBot="1">
       <c r="G25" s="6">
         <v>4</v>
       </c>
-      <c r="H25" s="25" t="s">
+      <c r="H25" s="12" t="s">
         <v>25</v>
       </c>
-      <c r="I25" s="25"/>
-      <c r="J25" s="25"/>
-      <c r="K25" s="25"/>
-      <c r="L25" s="25"/>
-      <c r="M25" s="25"/>
-      <c r="N25" s="25"/>
-      <c r="O25" s="25"/>
-      <c r="P25" s="26"/>
+      <c r="I25" s="12"/>
+      <c r="J25" s="12"/>
+      <c r="K25" s="12"/>
+      <c r="L25" s="12"/>
+      <c r="M25" s="12"/>
+      <c r="N25" s="12"/>
+      <c r="O25" s="12"/>
+      <c r="P25" s="13"/>
     </row>
     <row r="26" spans="7:16">
-      <c r="G26" s="19">
+      <c r="G26" s="21">
         <v>5</v>
       </c>
-      <c r="H26" s="33" t="s">
+      <c r="H26" s="28" t="s">
         <v>26</v>
       </c>
-      <c r="I26" s="33"/>
-      <c r="J26" s="33"/>
-      <c r="K26" s="33"/>
-      <c r="L26" s="33"/>
-      <c r="M26" s="33"/>
-      <c r="N26" s="33"/>
-      <c r="O26" s="33"/>
-      <c r="P26" s="34"/>
+      <c r="I26" s="28"/>
+      <c r="J26" s="28"/>
+      <c r="K26" s="28"/>
+      <c r="L26" s="28"/>
+      <c r="M26" s="28"/>
+      <c r="N26" s="28"/>
+      <c r="O26" s="28"/>
+      <c r="P26" s="29"/>
     </row>
     <row r="27" spans="7:16">
-      <c r="G27" s="32"/>
-      <c r="H27" s="35"/>
-      <c r="I27" s="35"/>
-      <c r="J27" s="35"/>
-      <c r="K27" s="35"/>
-      <c r="L27" s="35"/>
-      <c r="M27" s="35"/>
-      <c r="N27" s="35"/>
-      <c r="O27" s="35"/>
-      <c r="P27" s="36"/>
+      <c r="G27" s="27"/>
+      <c r="H27" s="30"/>
+      <c r="I27" s="30"/>
+      <c r="J27" s="30"/>
+      <c r="K27" s="30"/>
+      <c r="L27" s="30"/>
+      <c r="M27" s="30"/>
+      <c r="N27" s="30"/>
+      <c r="O27" s="30"/>
+      <c r="P27" s="31"/>
     </row>
     <row r="28" spans="7:16" ht="15.75" thickBot="1">
-      <c r="G28" s="20"/>
-      <c r="H28" s="37"/>
-      <c r="I28" s="37"/>
-      <c r="J28" s="37"/>
-      <c r="K28" s="37"/>
-      <c r="L28" s="37"/>
-      <c r="M28" s="37"/>
-      <c r="N28" s="37"/>
-      <c r="O28" s="37"/>
-      <c r="P28" s="38"/>
+      <c r="G28" s="22"/>
+      <c r="H28" s="32"/>
+      <c r="I28" s="32"/>
+      <c r="J28" s="32"/>
+      <c r="K28" s="32"/>
+      <c r="L28" s="32"/>
+      <c r="M28" s="32"/>
+      <c r="N28" s="32"/>
+      <c r="O28" s="32"/>
+      <c r="P28" s="33"/>
     </row>
     <row r="29" spans="7:16" ht="20.25" thickBot="1">
       <c r="G29" s="6">
         <v>6</v>
       </c>
-      <c r="H29" s="25" t="s">
+      <c r="H29" s="12" t="s">
         <v>27</v>
       </c>
-      <c r="I29" s="25"/>
-      <c r="J29" s="25"/>
-      <c r="K29" s="25"/>
-      <c r="L29" s="25"/>
-      <c r="M29" s="25"/>
-      <c r="N29" s="25"/>
-      <c r="O29" s="25"/>
-      <c r="P29" s="26"/>
+      <c r="I29" s="12"/>
+      <c r="J29" s="12"/>
+      <c r="K29" s="12"/>
+      <c r="L29" s="12"/>
+      <c r="M29" s="12"/>
+      <c r="N29" s="12"/>
+      <c r="O29" s="12"/>
+      <c r="P29" s="13"/>
     </row>
     <row r="30" spans="7:16">
-      <c r="G30" s="19">
+      <c r="G30" s="21">
         <v>7</v>
       </c>
-      <c r="H30" s="21" t="s">
+      <c r="H30" s="23" t="s">
         <v>34</v>
       </c>
-      <c r="I30" s="21"/>
-      <c r="J30" s="21"/>
-      <c r="K30" s="21"/>
-      <c r="L30" s="21"/>
-      <c r="M30" s="21"/>
-      <c r="N30" s="21"/>
-      <c r="O30" s="21"/>
-      <c r="P30" s="22"/>
+      <c r="I30" s="23"/>
+      <c r="J30" s="23"/>
+      <c r="K30" s="23"/>
+      <c r="L30" s="23"/>
+      <c r="M30" s="23"/>
+      <c r="N30" s="23"/>
+      <c r="O30" s="23"/>
+      <c r="P30" s="24"/>
     </row>
     <row r="31" spans="7:16" ht="15.75" thickBot="1">
-      <c r="G31" s="20"/>
-      <c r="H31" s="23"/>
-      <c r="I31" s="23"/>
-      <c r="J31" s="23"/>
-      <c r="K31" s="23"/>
-      <c r="L31" s="23"/>
-      <c r="M31" s="23"/>
-      <c r="N31" s="23"/>
-      <c r="O31" s="23"/>
-      <c r="P31" s="24"/>
+      <c r="G31" s="22"/>
+      <c r="H31" s="25"/>
+      <c r="I31" s="25"/>
+      <c r="J31" s="25"/>
+      <c r="K31" s="25"/>
+      <c r="L31" s="25"/>
+      <c r="M31" s="25"/>
+      <c r="N31" s="25"/>
+      <c r="O31" s="25"/>
+      <c r="P31" s="26"/>
     </row>
     <row r="32" spans="7:16" ht="19.5" customHeight="1" thickBot="1">
       <c r="G32" s="6">
         <v>8</v>
       </c>
-      <c r="H32" s="25" t="s">
+      <c r="H32" s="12" t="s">
         <v>28</v>
       </c>
-      <c r="I32" s="25"/>
-      <c r="J32" s="25"/>
-      <c r="K32" s="25"/>
-      <c r="L32" s="25"/>
-      <c r="M32" s="25"/>
-      <c r="N32" s="25"/>
-      <c r="O32" s="25"/>
-      <c r="P32" s="26"/>
+      <c r="I32" s="12"/>
+      <c r="J32" s="12"/>
+      <c r="K32" s="12"/>
+      <c r="L32" s="12"/>
+      <c r="M32" s="12"/>
+      <c r="N32" s="12"/>
+      <c r="O32" s="12"/>
+      <c r="P32" s="13"/>
     </row>
     <row r="33" spans="7:16" ht="20.25" thickBot="1">
       <c r="G33" s="5">
         <v>9</v>
       </c>
-      <c r="H33" s="27" t="s">
+      <c r="H33" s="41" t="s">
         <v>29</v>
       </c>
-      <c r="I33" s="27"/>
-      <c r="J33" s="27"/>
-      <c r="K33" s="27"/>
-      <c r="L33" s="27"/>
-      <c r="M33" s="27"/>
-      <c r="N33" s="27"/>
-      <c r="O33" s="27"/>
-      <c r="P33" s="28"/>
+      <c r="I33" s="41"/>
+      <c r="J33" s="41"/>
+      <c r="K33" s="41"/>
+      <c r="L33" s="41"/>
+      <c r="M33" s="41"/>
+      <c r="N33" s="41"/>
+      <c r="O33" s="41"/>
+      <c r="P33" s="42"/>
     </row>
     <row r="34" spans="7:16">
-      <c r="G34" s="29">
+      <c r="G34" s="43">
         <v>10</v>
       </c>
-      <c r="H34" s="30" t="s">
+      <c r="H34" s="44" t="s">
         <v>30</v>
       </c>
-      <c r="I34" s="30"/>
-      <c r="J34" s="30"/>
-      <c r="K34" s="30"/>
-      <c r="L34" s="30"/>
-      <c r="M34" s="30"/>
-      <c r="N34" s="30"/>
-      <c r="O34" s="30"/>
-      <c r="P34" s="31"/>
+      <c r="I34" s="44"/>
+      <c r="J34" s="44"/>
+      <c r="K34" s="44"/>
+      <c r="L34" s="44"/>
+      <c r="M34" s="44"/>
+      <c r="N34" s="44"/>
+      <c r="O34" s="44"/>
+      <c r="P34" s="45"/>
     </row>
     <row r="35" spans="7:16">
-      <c r="G35" s="12"/>
-      <c r="H35" s="13"/>
-      <c r="I35" s="13"/>
-      <c r="J35" s="13"/>
-      <c r="K35" s="13"/>
-      <c r="L35" s="13"/>
-      <c r="M35" s="13"/>
-      <c r="N35" s="13"/>
-      <c r="O35" s="13"/>
-      <c r="P35" s="14"/>
+      <c r="G35" s="34"/>
+      <c r="H35" s="35"/>
+      <c r="I35" s="35"/>
+      <c r="J35" s="35"/>
+      <c r="K35" s="35"/>
+      <c r="L35" s="35"/>
+      <c r="M35" s="35"/>
+      <c r="N35" s="35"/>
+      <c r="O35" s="35"/>
+      <c r="P35" s="36"/>
     </row>
     <row r="36" spans="7:16">
-      <c r="G36" s="12">
+      <c r="G36" s="34">
         <v>11</v>
       </c>
-      <c r="H36" s="13" t="s">
+      <c r="H36" s="35" t="s">
         <v>31</v>
       </c>
-      <c r="I36" s="13"/>
-      <c r="J36" s="13"/>
-      <c r="K36" s="13"/>
-      <c r="L36" s="13"/>
-      <c r="M36" s="13"/>
-      <c r="N36" s="13"/>
-      <c r="O36" s="13"/>
-      <c r="P36" s="14"/>
+      <c r="I36" s="35"/>
+      <c r="J36" s="35"/>
+      <c r="K36" s="35"/>
+      <c r="L36" s="35"/>
+      <c r="M36" s="35"/>
+      <c r="N36" s="35"/>
+      <c r="O36" s="35"/>
+      <c r="P36" s="36"/>
     </row>
     <row r="37" spans="7:16">
-      <c r="G37" s="12"/>
-      <c r="H37" s="13"/>
-      <c r="I37" s="13"/>
-      <c r="J37" s="13"/>
-      <c r="K37" s="13"/>
-      <c r="L37" s="13"/>
-      <c r="M37" s="13"/>
-      <c r="N37" s="13"/>
-      <c r="O37" s="13"/>
-      <c r="P37" s="14"/>
+      <c r="G37" s="34"/>
+      <c r="H37" s="35"/>
+      <c r="I37" s="35"/>
+      <c r="J37" s="35"/>
+      <c r="K37" s="35"/>
+      <c r="L37" s="35"/>
+      <c r="M37" s="35"/>
+      <c r="N37" s="35"/>
+      <c r="O37" s="35"/>
+      <c r="P37" s="36"/>
     </row>
     <row r="38" spans="7:16" ht="19.5">
       <c r="G38" s="7">
         <v>12</v>
       </c>
-      <c r="H38" s="15" t="s">
+      <c r="H38" s="37" t="s">
         <v>32</v>
       </c>
-      <c r="I38" s="15"/>
-      <c r="J38" s="15"/>
-      <c r="K38" s="15"/>
-      <c r="L38" s="15"/>
-      <c r="M38" s="15"/>
-      <c r="N38" s="15"/>
-      <c r="O38" s="15"/>
-      <c r="P38" s="16"/>
+      <c r="I38" s="37"/>
+      <c r="J38" s="37"/>
+      <c r="K38" s="37"/>
+      <c r="L38" s="37"/>
+      <c r="M38" s="37"/>
+      <c r="N38" s="37"/>
+      <c r="O38" s="37"/>
+      <c r="P38" s="38"/>
     </row>
     <row r="39" spans="7:16" ht="20.25" thickBot="1">
       <c r="G39" s="8">
         <v>13</v>
       </c>
-      <c r="H39" s="17" t="s">
+      <c r="H39" s="39" t="s">
         <v>33</v>
       </c>
-      <c r="I39" s="17"/>
-      <c r="J39" s="17"/>
-      <c r="K39" s="17"/>
-      <c r="L39" s="17"/>
-      <c r="M39" s="17"/>
-      <c r="N39" s="17"/>
-      <c r="O39" s="17"/>
-      <c r="P39" s="18"/>
+      <c r="I39" s="39"/>
+      <c r="J39" s="39"/>
+      <c r="K39" s="39"/>
+      <c r="L39" s="39"/>
+      <c r="M39" s="39"/>
+      <c r="N39" s="39"/>
+      <c r="O39" s="39"/>
+      <c r="P39" s="40"/>
     </row>
   </sheetData>
   <mergeCells count="20">
-    <mergeCell ref="H29:P29"/>
-    <mergeCell ref="H19:P19"/>
-    <mergeCell ref="H20:P20"/>
-    <mergeCell ref="H21:P21"/>
-    <mergeCell ref="H22:P22"/>
-    <mergeCell ref="G23:G24"/>
-    <mergeCell ref="H23:P24"/>
-    <mergeCell ref="H25:P25"/>
-    <mergeCell ref="G26:G28"/>
-    <mergeCell ref="H26:P28"/>
     <mergeCell ref="G36:G37"/>
     <mergeCell ref="H36:P37"/>
     <mergeCell ref="H38:P38"/>
@@ -2671,6 +2661,16 @@
     <mergeCell ref="H33:P33"/>
     <mergeCell ref="G34:G35"/>
     <mergeCell ref="H34:P35"/>
+    <mergeCell ref="G23:G24"/>
+    <mergeCell ref="H23:P24"/>
+    <mergeCell ref="H25:P25"/>
+    <mergeCell ref="G26:G28"/>
+    <mergeCell ref="H26:P28"/>
+    <mergeCell ref="H29:P29"/>
+    <mergeCell ref="H19:P19"/>
+    <mergeCell ref="H20:P20"/>
+    <mergeCell ref="H21:P21"/>
+    <mergeCell ref="H22:P22"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <drawing r:id="rId1"/>
